--- a/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>BIOR</t>
   </si>
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -747,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
@@ -756,31 +760,34 @@
         <v>100</v>
       </c>
       <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
-      </c>
-      <c r="N8" s="3">
-        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -811,23 +818,26 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>22200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,23 +868,26 @@
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>-22000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-21300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-23500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E12" s="3">
         <v>6000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5800</v>
       </c>
       <c r="G12" s="3">
         <v>5800</v>
       </c>
       <c r="H12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I12" s="3">
         <v>5900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1021,20 +1041,23 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>7600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>3600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,55 +1122,59 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E17" s="3">
         <v>14900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>30700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>30100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1152,46 +1182,49 @@
         <v>5</v>
       </c>
       <c r="E18" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-15500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-35600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-31400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-30600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-30100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24600</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1218,46 +1252,49 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-60500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>17500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1265,51 +1302,54 @@
         <v>5</v>
       </c>
       <c r="E21" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-14600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-80300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-33300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-38200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-45800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-29400</v>
       </c>
       <c r="P21" s="3">
         <v>-29400</v>
       </c>
       <c r="Q21" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="R21" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="E22" s="3">
         <v>2700</v>
@@ -1318,7 +1358,7 @@
         <v>2700</v>
       </c>
       <c r="G22" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="H22" s="3">
         <v>2800</v>
@@ -1327,10 +1367,10 @@
         <v>2800</v>
       </c>
       <c r="J22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K22" s="3">
         <v>2200</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3500</v>
       </c>
       <c r="L22" s="3">
         <v>3500</v>
@@ -1339,113 +1379,122 @@
         <v>3500</v>
       </c>
       <c r="N22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O22" s="3">
         <v>2700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>2500</v>
       </c>
       <c r="P22" s="3">
         <v>2500</v>
       </c>
       <c r="Q22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R22" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-82900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-41400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-49800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-32700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-37700</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-82800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-36900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-41400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-50000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-32700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-82800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-36900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-50000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-33100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1644,43 +1705,46 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>9800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-10100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-6900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-37100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-14800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-25600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-13900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1782,93 +1852,99 @@
         <v>5</v>
       </c>
       <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>60500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-17500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-92900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-43700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-78500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-75500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-47100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-92900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-43700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-78500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-75500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-47100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,55 +2137,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E41" s="3">
         <v>26500</v>
-      </c>
-      <c r="E41" s="3">
-        <v>30500</v>
       </c>
       <c r="F41" s="3">
         <v>30500</v>
       </c>
       <c r="G41" s="3">
+        <v>30500</v>
+      </c>
+      <c r="H41" s="3">
         <v>37100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>88400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>54100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>65300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>60000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>113600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,8 +2235,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2166,34 +2259,37 @@
         <v>800</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>30000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2218,123 +2314,132 @@
       <c r="J44" s="3">
         <v>0</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>12400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E45" s="3">
         <v>6600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>43300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E46" s="3">
         <v>33900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>46400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>60100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>75000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>98800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>93000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>114300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>101200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>126300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>93000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>160000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>83800</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2353,8 +2458,8 @@
       <c r="H47" s="3">
         <v>6000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+      <c r="I47" s="3">
+        <v>6000</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -2368,8 +2473,8 @@
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2380,55 +2485,61 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2453,29 +2564,32 @@
       <c r="J49" s="3">
         <v>6100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
+      <c r="K49" s="3">
+        <v>6100</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3">
         <v>9800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,19 +2685,22 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
@@ -2589,25 +2709,25 @@
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E54" s="3">
         <v>49700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>62600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>77100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>86700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>128600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>154400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>186400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,55 +2877,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>5000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>15700</v>
       </c>
       <c r="P57" s="3">
         <v>15700</v>
       </c>
       <c r="Q57" s="3">
+        <v>15700</v>
+      </c>
+      <c r="R57" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2805,8 +2939,8 @@
       <c r="E58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -2821,216 +2955,231 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E59" s="3">
         <v>32600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>41300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>95200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>63900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>71000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>78400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>56400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E60" s="3">
         <v>37700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>103300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>80100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>72700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>87300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>94900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E61" s="3">
         <v>128600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>128200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>127800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>127400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>127100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>126700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>126400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>157300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>158800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>161900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>160200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>72600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>72200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>71800</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>36500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>153500</v>
+      </c>
+      <c r="E66" s="3">
         <v>170600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>158200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>155800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>160100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>173200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>179900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>193800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>274600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>259600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>254100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>261400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>180000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>203600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>195700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,10 +3543,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-935500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-862100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-844300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-826800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-813100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-808000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-802500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-788700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-695800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-652100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-573500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-541300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-465700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-418700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-365600</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-120900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-105000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-102300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-97400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-96100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-93200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-85000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-177000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-139600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-125500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-107000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-60400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-84900</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-92900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-43700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-78500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-75500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-47100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,19 +4022,20 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -3845,34 +4044,37 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1300</v>
       </c>
       <c r="O83" s="3">
         <v>1300</v>
       </c>
       <c r="P83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-40000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-43200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-35700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-48600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-70100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-51300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4184,43 +4405,46 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4540,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4325,43 +4555,46 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-200</v>
       </c>
       <c r="H94" s="3">
         <v>-200</v>
       </c>
       <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4810,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E100" s="3">
         <v>7600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>73500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>31800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>37500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>104000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>116000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-53600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>102000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>BIOR</t>
   </si>
@@ -656,93 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
+      <c r="D8" s="3">
+        <v>500</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -754,40 +761,46 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3">
         <v>400</v>
-      </c>
-      <c r="L8" s="3">
-        <v>200</v>
-      </c>
-      <c r="M8" s="3">
-        <v>500</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
       </c>
       <c r="O8" s="3">
+        <v>500</v>
+      </c>
+      <c r="P8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -821,23 +834,29 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>22200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>21400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>23600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>21800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,23 +890,29 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>-22000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-21300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-21800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,58 +931,66 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F12" s="3">
         <v>10500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>6000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>7200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>5800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>6600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>8500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>12200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>13400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>11700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>11200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>13000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>12200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,13 +1039,19 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>1900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1044,20 +1083,26 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>7600</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q14" s="3">
+        <v>7600</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>3600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1151,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1174,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F17" s="3">
         <v>23300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>14900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>15500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>13800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>14300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>20000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>20600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>30700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>36100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>31600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>33500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>30700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>30100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="3">
+        <v>-17500</v>
       </c>
       <c r="E18" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-14900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-15500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-13900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-14200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-19900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-20200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-30500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-35600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-31400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-33400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-30100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-24600</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,208 +1308,234 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>16100</v>
       </c>
       <c r="E20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>10200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>8200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-60500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>17500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-13700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>-1300</v>
       </c>
       <c r="E21" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-70700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-14900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-14600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-10400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-11700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-11400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-80300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-33300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-38200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-12700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-45800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-29400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F22" s="3">
         <v>2600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2700</v>
       </c>
       <c r="G22" s="3">
         <v>2700</v>
       </c>
       <c r="H22" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="I22" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="J22" s="3">
         <v>2800</v>
       </c>
       <c r="K22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M22" s="3">
         <v>2200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>3500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>3500</v>
       </c>
       <c r="N22" s="3">
         <v>3500</v>
       </c>
       <c r="O22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>2700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>2500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-73500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-17800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-17400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-13200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-14700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-14500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-82900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-36900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-41400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-17500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-49800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-32700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1452,49 +1543,55 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-37700</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1640,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-73500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-17800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-17400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-13500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-14900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-14500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-82800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-36900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-41400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-17500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-50000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-32700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-73500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-17800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-17400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-13500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-14900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-14500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-82800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-36900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-41400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-17500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-50000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-33000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,58 +1808,70 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>9800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-10100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-6900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-37100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-14800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-25600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-20100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1920,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1976,126 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>-16100</v>
       </c>
       <c r="E32" s="3">
+        <v>500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>47500</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-10200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-8200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>60500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-17500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>13700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-73500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-17800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-17400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-13700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-13800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-92900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-43700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-78500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-32300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-75500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-47100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-53100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2144,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-73500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-17800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-17400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-13700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-13800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-92900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-43700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-78500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-32300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-75500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-47100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-53100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2287,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,58 +2309,66 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F41" s="3">
         <v>12600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>26500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>30500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>30500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>37100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>48500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>67200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>88400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>54100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>66000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>65300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>92100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>60000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>113600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,8 +2417,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2262,34 +2447,40 @@
         <v>800</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K43" s="3">
+        <v>800</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>13200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>13400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>30000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2317,137 +2508,155 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3" t="s">
+      <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>12400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>12200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>10400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>10200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5900</v>
+        <v>2400</v>
       </c>
       <c r="E45" s="3">
-        <v>6600</v>
+        <v>3000</v>
       </c>
       <c r="F45" s="3">
         <v>5900</v>
       </c>
       <c r="G45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="I45" s="3">
         <v>6800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>8500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>10800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>7800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>9700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>36900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>43300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>27600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>9200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>6100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F46" s="3">
         <v>19200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>33900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>37200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>38100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>46400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>60100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>75000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>98800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>93000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>114300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>101200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>126300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>93000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>160000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>83800</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="F47" s="3">
         <v>6000</v>
@@ -2461,11 +2670,11 @@
       <c r="I47" s="3">
         <v>6000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
+      <c r="J47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K47" s="3">
+        <v>6000</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>5</v>
@@ -2476,11 +2685,11 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2488,58 +2697,70 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>17400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>8100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>16100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>15700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2567,29 +2788,35 @@
       <c r="K49" s="3">
         <v>6100</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="L49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="M49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>9800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>9900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>10300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>10500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2865,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2921,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2697,49 +2936,55 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
       <c r="J52" s="3">
+        <v>200</v>
+      </c>
+      <c r="K52" s="3">
+        <v>200</v>
+      </c>
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>13900</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
       <c r="Q52" s="3">
-        <v>200</v>
+        <v>13900</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>200</v>
+      </c>
+      <c r="T52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +3033,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>31200</v>
+      </c>
+      <c r="F54" s="3">
         <v>34700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>49700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>53200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>53500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>62600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>77100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>86700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>108800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>97700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>119900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>128600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>154400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>119600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>186400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +3115,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,75 +3137,83 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>14600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>15600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>15700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>15700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>5</v>
+      <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2000</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2958,228 +3225,258 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>58200</v>
+      </c>
+      <c r="F59" s="3">
         <v>65600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>32600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>21700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>19700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>25000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>36300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>41300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>52900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>95200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>70900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>63900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>55000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>71000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>78400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>56400</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F60" s="3">
         <v>69500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>37700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>25100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>27400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>40600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>46700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>61600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>103300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>85600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>80100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>72700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>87300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>94900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>43700</v>
+      </c>
+      <c r="F61" s="3">
         <v>80400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>128600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>128200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>127800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>127400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>127100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>126700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>126400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>157300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>158800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>161900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>160200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>72600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>72200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>71800</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F62" s="3">
         <v>3600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>14100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>15100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>12100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>28600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>20100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>36500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3525,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3581,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3637,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>132600</v>
+      </c>
+      <c r="F66" s="3">
         <v>153500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>170600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>158200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>155800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>160100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>173200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>179900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>193800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>274600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>259600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>254100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>261400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>180000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>203600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>195700</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3719,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3771,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3827,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,10 +3881,16 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3939,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-955100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-951000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-935500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-862100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-844300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-826800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-813100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-808000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-802500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-788700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-695800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-652100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-573500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-541300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-465700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-418700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-365600</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +4051,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +4107,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +4163,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-101400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-118800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-120900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-105000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-102300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-97400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-96100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-93200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-85000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-177000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-139600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-125500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-107000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-60400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-17200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-84900</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4275,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-73500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-17800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-17400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-13700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-13800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-92900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-43700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-78500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-32300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-75500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-47100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-53100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4418,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4032,7 +4429,7 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -4041,40 +4438,46 @@
         <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
       </c>
       <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
+        <v>200</v>
+      </c>
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>-300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4526,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4582,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4638,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4694,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4750,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-11000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-11600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-12100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-11000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-9800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-19600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-24000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-40000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-43200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-35700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-48600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-70100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-51300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-13500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4832,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4402,49 +4843,55 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4940,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4996,70 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +5078,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4663,8 +5130,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +5186,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5242,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5298,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>7600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>12100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>73500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>31800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>37500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>22200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>104000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>116000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4913,54 +5410,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-13900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-18700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-21200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>33700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-11900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-26800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>32100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>102000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-21400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>BIOR</t>
   </si>
@@ -656,104 +656,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
@@ -767,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
@@ -776,31 +780,34 @@
         <v>100</v>
       </c>
       <c r="M8" s="3">
+        <v>100</v>
+      </c>
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>100</v>
       </c>
       <c r="R8" s="3">
         <v>100</v>
       </c>
       <c r="S8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -840,23 +847,26 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>22200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>23600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -896,23 +906,26 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-21300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-23500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-21800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E12" s="3">
         <v>7000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5800</v>
       </c>
       <c r="J12" s="3">
         <v>5800</v>
       </c>
       <c r="K12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L12" s="3">
         <v>5900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,16 +1062,19 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1089,20 +1109,23 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>7600</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3600</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E17" s="3">
         <v>18000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>30700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>30100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-30500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-35600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-30600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-30100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-24600</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,134 +1343,141 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E20" s="3">
         <v>16100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-47500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-60500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>17500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-70700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-14900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-14600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-80300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-33300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-38200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-45800</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-29400</v>
       </c>
       <c r="S21" s="3">
         <v>-29400</v>
       </c>
       <c r="T21" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="U21" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2700</v>
       </c>
       <c r="H22" s="3">
         <v>2700</v>
@@ -1446,7 +1486,7 @@
         <v>2700</v>
       </c>
       <c r="J22" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="K22" s="3">
         <v>2800</v>
@@ -1455,10 +1495,10 @@
         <v>2800</v>
       </c>
       <c r="M22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N22" s="3">
         <v>2200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>3500</v>
       </c>
       <c r="O22" s="3">
         <v>3500</v>
@@ -1467,131 +1507,140 @@
         <v>3500</v>
       </c>
       <c r="Q22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R22" s="3">
         <v>2700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>2500</v>
       </c>
       <c r="S22" s="3">
         <v>2500</v>
       </c>
       <c r="T22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="U22" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-73500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-82900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-41400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-49800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-33100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-32700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-37700</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-73500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-82800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-36900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-41400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-50000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-33100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-32700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-82800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-36900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-41400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-50000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-33100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-33000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,20 +1872,23 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3">
         <v>200</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -1835,43 +1896,46 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>9800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-10100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-6900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-37100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-25600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-13900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-20100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>47500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>60500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-92900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-43700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-78500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-75500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-47100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-53100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-92900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-43700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-78500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-75500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-47100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-53100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
         <v>10800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>30500</v>
       </c>
       <c r="I41" s="3">
         <v>30500</v>
       </c>
       <c r="J41" s="3">
+        <v>30500</v>
+      </c>
+      <c r="K41" s="3">
         <v>37100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>48500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>67200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>88400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>66000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>92100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>60000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>113600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,8 +2513,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2453,34 +2546,37 @@
         <v>800</v>
       </c>
       <c r="L43" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>30000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2514,141 +2610,150 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
+      <c r="N44" s="3">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3">
         <v>12400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>10400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>43300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E46" s="3">
         <v>14100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>60100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>98800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>93000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>114300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>101200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>126300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>93000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>160000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>83800</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2656,10 +2761,10 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>3000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>6000</v>
       </c>
       <c r="G47" s="3">
         <v>6000</v>
@@ -2676,8 +2781,8 @@
       <c r="K47" s="3">
         <v>6000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
+      <c r="L47" s="3">
+        <v>6000</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
@@ -2691,8 +2796,8 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2703,64 +2808,70 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>16100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2794,29 +2905,32 @@
       <c r="M49" s="3">
         <v>6100</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
+      <c r="N49" s="3">
+        <v>6100</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P49" s="3">
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="3">
         <v>9800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,13 +3044,16 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E52" s="3">
         <v>300</v>
@@ -2942,13 +3062,13 @@
         <v>300</v>
       </c>
       <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
@@ -2957,25 +3077,25 @@
         <v>200</v>
       </c>
       <c r="L52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3">
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13900</v>
-      </c>
-      <c r="R52" s="3">
-        <v>200</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E54" s="3">
         <v>23000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>49700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>53200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>53500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>62600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>77100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>86700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>108800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>128600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>154400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>119600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>186400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,75 +3269,79 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17400</v>
-      </c>
-      <c r="R57" s="3">
-        <v>15700</v>
       </c>
       <c r="S57" s="3">
         <v>15700</v>
       </c>
       <c r="T57" s="3">
+        <v>15700</v>
+      </c>
+      <c r="U57" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E58" s="3">
         <v>2000</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>5</v>
+      <c r="F58" s="3">
+        <v>2000</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>5</v>
@@ -3215,8 +3349,8 @@
       <c r="H58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3231,252 +3365,267 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E59" s="3">
         <v>44200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>58200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>65600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>36300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>52900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>95200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>63900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>55000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>71000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>78400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56400</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E60" s="3">
         <v>51100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>61600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>103300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>85600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>80100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>72700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>87300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>94900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E61" s="3">
         <v>43300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>43700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>80400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>128600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>128200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>127800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>127400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>127100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>126700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>126400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>157300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>158800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>161900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>160200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>72600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>72200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>71800</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E62" s="3">
         <v>28800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>28600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>36500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107600</v>
+      </c>
+      <c r="E66" s="3">
         <v>123200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>132600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>153500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>170600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>158200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>155800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>160100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>173200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>179900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>193800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>274600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>259600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>254100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>261400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>180000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>203600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>195700</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,10 +4055,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-948700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-955100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-951000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-935500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-862100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-844300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-826800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-813100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-808000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-802500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-788700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-695800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-652100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-573500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-541300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-465700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-418700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-365600</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-89300</v>
+      </c>
+      <c r="E76" s="3">
         <v>-100200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-101400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-118800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-120900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-105000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-102300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-97400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-96100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-93200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-85000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-177000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-139600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-125500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-107000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-60400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-17200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-84900</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-92900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-43700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-78500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-75500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-47100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-53100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4435,13 +4634,13 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -4450,34 +4649,37 @@
         <v>200</v>
       </c>
       <c r="L83" s="3">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1300</v>
       </c>
       <c r="R83" s="3">
         <v>1300</v>
       </c>
       <c r="S83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-40000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-43200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-35700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-48600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-70100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-51300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,20 +5054,21 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -4855,43 +5076,46 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,20 +5229,23 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2500</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -5023,43 +5253,46 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-200</v>
       </c>
       <c r="K94" s="3">
         <v>-200</v>
       </c>
       <c r="L94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E100" s="3">
         <v>5100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>13900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>73500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>31800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>37500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>22200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>104000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>116000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-6600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>33700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>32100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-53600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>102000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-21400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIOR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>BIOR</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -774,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
@@ -783,31 +787,34 @@
         <v>100</v>
       </c>
       <c r="N8" s="3">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>200</v>
-      </c>
-      <c r="R8" s="3">
-        <v>100</v>
       </c>
       <c r="S8" s="3">
         <v>100</v>
       </c>
       <c r="T8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -850,34 +857,37 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>22200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>23600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26600</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>500</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>5</v>
@@ -885,11 +895,11 @@
       <c r="H10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -909,23 +919,26 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>-22000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-21300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-23500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-21800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E12" s="3">
         <v>7700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7200</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5800</v>
       </c>
       <c r="K12" s="3">
         <v>5800</v>
       </c>
       <c r="L12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="M12" s="3">
         <v>5900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11200</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,31 +1082,34 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>300</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
+        <v>10700</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>200</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="H14" s="3">
+        <v>53200</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="J14" s="3">
+        <v>100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1112,43 +1132,46 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>7600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>3600</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16400</v>
+        <v>16300</v>
       </c>
       <c r="E17" s="3">
-        <v>18000</v>
+        <v>16100</v>
       </c>
       <c r="F17" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G17" s="3">
         <v>13300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>30700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>30700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>30100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-16100</v>
+        <v>-16200</v>
       </c>
       <c r="E18" s="3">
-        <v>-17500</v>
+        <v>-15800</v>
       </c>
       <c r="F18" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="G18" s="3">
         <v>-13300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-20200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-30500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-33400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-30600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-30100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-24600</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,143 +1377,150 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>23200</v>
+        <v>-6700</v>
       </c>
       <c r="E20" s="3">
-        <v>16100</v>
+        <v>-22900</v>
       </c>
       <c r="F20" s="3">
-        <v>-500</v>
+        <v>-14300</v>
       </c>
       <c r="G20" s="3">
-        <v>-47500</v>
+        <v>500</v>
       </c>
       <c r="H20" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M20" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>8200</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-60500</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R20" s="3">
+        <v>17500</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>10200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>8200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-60500</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>17500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>7200</v>
       </c>
-      <c r="E21" s="3">
-        <v>-1300</v>
-      </c>
       <c r="F21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G21" s="3">
         <v>-13800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-70700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-14900</v>
       </c>
-      <c r="I21" s="3">
-        <v>-14600</v>
-      </c>
       <c r="J21" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-10400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-80300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-33300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-38200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-12700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-45800</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-29400</v>
       </c>
       <c r="T21" s="3">
         <v>-29400</v>
       </c>
       <c r="U21" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="V21" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2700</v>
       </c>
       <c r="I22" s="3">
         <v>2700</v>
@@ -1489,7 +1529,7 @@
         <v>2700</v>
       </c>
       <c r="K22" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="L22" s="3">
         <v>2800</v>
@@ -1498,10 +1538,10 @@
         <v>2800</v>
       </c>
       <c r="N22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O22" s="3">
         <v>2200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>3500</v>
       </c>
       <c r="P22" s="3">
         <v>3500</v>
@@ -1510,137 +1550,146 @@
         <v>3500</v>
       </c>
       <c r="R22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S22" s="3">
         <v>2700</v>
-      </c>
-      <c r="S22" s="3">
-        <v>2500</v>
       </c>
       <c r="T22" s="3">
         <v>2500</v>
       </c>
       <c r="U22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="V22" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E23" s="3">
         <v>6400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-73500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-82900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-41400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-49800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-33100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-32700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-37700</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E26" s="3">
         <v>6500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-73500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-82800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-36900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-50000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-33100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-32700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E27" s="3">
         <v>6500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
-        <v>-15600</v>
-      </c>
       <c r="G27" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="H27" s="3">
         <v>-73500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-82800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-36900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-50000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-33100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-33000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,23 +1933,26 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>200</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1899,43 +1960,46 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>9800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-10100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-6900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-37100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-14800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-25600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-13900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-20100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-27900</v>
       </c>
     </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-23200</v>
+        <v>6700</v>
       </c>
       <c r="E32" s="3">
-        <v>-16100</v>
+        <v>22900</v>
       </c>
       <c r="F32" s="3">
-        <v>500</v>
+        <v>14300</v>
       </c>
       <c r="G32" s="3">
-        <v>47500</v>
+        <v>-500</v>
       </c>
       <c r="H32" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>900</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="O32" s="3">
+        <v>60500</v>
+      </c>
+      <c r="P32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="S32" s="3">
+        <v>13700</v>
+      </c>
+      <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>60500</v>
-      </c>
-      <c r="O32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>13700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E33" s="3">
         <v>6500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-73500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-92900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-43700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-78500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-32300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-75500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-47100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-53100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E35" s="3">
         <v>6500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-73500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-92900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-43700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-78500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-32300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-75500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-47100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-53100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2484,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E41" s="3">
         <v>5300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>30500</v>
       </c>
       <c r="J41" s="3">
         <v>30500</v>
       </c>
       <c r="K41" s="3">
+        <v>30500</v>
+      </c>
+      <c r="L41" s="3">
         <v>37100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>48500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>67200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>66000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>65300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>60000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>113600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,13 +2606,16 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E43" s="3">
         <v>800</v>
@@ -2549,57 +2642,60 @@
         <v>800</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>30000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2613,161 +2709,170 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3">
         <v>12400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>2400</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>5900</v>
+        <v>600</v>
       </c>
       <c r="H45" s="3">
-        <v>6600</v>
+        <v>2700</v>
       </c>
       <c r="I45" s="3">
-        <v>5900</v>
+        <v>2700</v>
       </c>
       <c r="J45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K45" s="3">
         <v>6800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>43300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E46" s="3">
         <v>9200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>60100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>98800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>93000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>114300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>101200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>126300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>93000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>160000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>83800</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3">
         <v>3000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>6000</v>
       </c>
       <c r="H47" s="3">
         <v>6000</v>
@@ -2784,8 +2889,8 @@
       <c r="L47" s="3">
         <v>6000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
+      <c r="M47" s="3">
+        <v>6000</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
@@ -2799,8 +2904,8 @@
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2811,67 +2916,73 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2908,29 +3019,32 @@
       <c r="N49" s="3">
         <v>6100</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
+      <c r="O49" s="3">
+        <v>6100</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R49" s="3">
         <v>9800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,16 +3164,19 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
-      </c>
-      <c r="E52" s="3">
-        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -3065,13 +3185,13 @@
         <v>300</v>
       </c>
       <c r="H52" s="3">
+        <v>300</v>
+      </c>
+      <c r="I52" s="3">
         <v>500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -3080,25 +3200,25 @@
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>300</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
       <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>200</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E54" s="3">
         <v>18300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>34700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>53200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>53500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>86700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>108800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>119900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>128600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>154400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>119600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>186400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,90 +3400,94 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E57" s="3">
         <v>7500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17400</v>
-      </c>
-      <c r="S57" s="3">
-        <v>15700</v>
       </c>
       <c r="T57" s="3">
         <v>15700</v>
       </c>
       <c r="U57" s="3">
+        <v>15700</v>
+      </c>
+      <c r="V57" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+      <c r="I58" s="3">
+        <v>2300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3368,264 +3502,279 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>36600</v>
+        <v>57400</v>
       </c>
       <c r="E59" s="3">
-        <v>44200</v>
+        <v>24600</v>
       </c>
       <c r="F59" s="3">
-        <v>58200</v>
+        <v>32900</v>
       </c>
       <c r="G59" s="3">
-        <v>65600</v>
+        <v>49900</v>
       </c>
       <c r="H59" s="3">
-        <v>32600</v>
+        <v>52800</v>
       </c>
       <c r="I59" s="3">
-        <v>21700</v>
+        <v>22100</v>
       </c>
       <c r="J59" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K59" s="3">
         <v>19700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>36300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>52900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>63900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>55000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>78400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>56400</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>120600</v>
+      </c>
+      <c r="E60" s="3">
         <v>46000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>51100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>63000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>69500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>61600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>103300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>85600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>80100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>87300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>94900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>74200</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>43800</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>43300</v>
+        <v>44200</v>
       </c>
       <c r="F61" s="3">
-        <v>43700</v>
+        <v>43900</v>
       </c>
       <c r="G61" s="3">
-        <v>80400</v>
+        <v>44600</v>
       </c>
       <c r="H61" s="3">
-        <v>128600</v>
+        <v>81400</v>
       </c>
       <c r="I61" s="3">
-        <v>128200</v>
+        <v>129700</v>
       </c>
       <c r="J61" s="3">
+        <v>129500</v>
+      </c>
+      <c r="K61" s="3">
         <v>127800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>127400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>127100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>126700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>126400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>157300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>158800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>161900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>160200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>72600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>72200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>71800</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>17800</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>28800</v>
+        <v>17400</v>
       </c>
       <c r="F62" s="3">
-        <v>25900</v>
+        <v>28200</v>
       </c>
       <c r="G62" s="3">
+        <v>25100</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>28600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>36500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E66" s="3">
         <v>107600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>123200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>132600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>153500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>170600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>158200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>155800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>160100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>173200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>179900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>193800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>274600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>259600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>254100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>261400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>180000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>203600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>195700</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,10 +4226,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-967100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-948700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-955100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-951000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-935500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-862100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-844300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-826800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-813100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-808000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-802500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-788700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-695800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-652100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-573500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-541300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-465700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-418700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-365600</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-106600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-89300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-100200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-101400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-118800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-120900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-105000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-102300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-97400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-96100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-93200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-85000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-177000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-139600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-125500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-107000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-60400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-17200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-84900</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E81" s="3">
         <v>6500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-73500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-92900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-43700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-78500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-32300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-75500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-47100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-53100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4628,22 +4827,22 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -4652,34 +4851,37 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1300</v>
       </c>
       <c r="S83" s="3">
         <v>1300</v>
       </c>
       <c r="T83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12500</v>
       </c>
-      <c r="F89" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
         <v>-11000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-40000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-43200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-48600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-70100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-51300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-30900</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5275,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,22 +5459,25 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3000</v>
       </c>
-      <c r="F94" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -5256,43 +5486,46 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-200</v>
       </c>
       <c r="L94" s="3">
         <v>-200</v>
       </c>
       <c r="M94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,31 +5547,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,90 +5793,96 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E100" s="3">
         <v>5600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5100</v>
       </c>
-      <c r="F100" s="3">
-        <v>13900</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
         <v>-2800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>73500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>31800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>37500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>22200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>104000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>116000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
-        <v>2600</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-13900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-6600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>33700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-53600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>102000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-21400</v>
       </c>
     </row>
